--- a/data/base/Backlog_22.xlsx
+++ b/data/base/Backlog_22.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DE6584-2DEC-4511-B78D-17687BB0F09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C31F4BD-311D-4993-90D1-91D261A07022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
   </bookViews>
   <sheets>
     <sheet name="SPN" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ITI!$A$1:$K$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SPN!$A$1:$K$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SPN!$A$1:$K$31</definedName>
   </definedNames>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -627,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05C2F3D6-88A9-4A6C-8904-EE71E1E2FD4B}">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="6" customWidth="1"/>
@@ -814,12 +814,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" s="5">
         <v>2026</v>
@@ -834,10 +834,10 @@
         <v>46185</v>
       </c>
       <c r="G6" s="5">
-        <v>18346</v>
+        <v>18276</v>
       </c>
       <c r="H6" s="12">
-        <v>46178.538541666669</v>
+        <v>46177.708333333336</v>
       </c>
       <c r="I6" s="16">
         <v>46181</v>
@@ -854,7 +854,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C7" s="5">
         <v>2026</v>
@@ -869,10 +869,10 @@
         <v>46185</v>
       </c>
       <c r="G7" s="5">
-        <v>18276</v>
+        <v>16133</v>
       </c>
       <c r="H7" s="12">
-        <v>46177.708333333336</v>
+        <v>46163.999305555553</v>
       </c>
       <c r="I7" s="16">
         <v>46181</v>
@@ -880,7 +880,7 @@
       <c r="J7" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -904,10 +904,10 @@
         <v>46185</v>
       </c>
       <c r="G8" s="5">
-        <v>16133</v>
+        <v>18451</v>
       </c>
       <c r="H8" s="12">
-        <v>46163.999305555553</v>
+        <v>46181.445833333331</v>
       </c>
       <c r="I8" s="16">
         <v>46181</v>
@@ -915,18 +915,18 @@
       <c r="J8" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="5">
+      <c r="B9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="11">
         <v>2026</v>
       </c>
       <c r="D9" s="10">
@@ -938,11 +938,11 @@
       <c r="F9" s="16">
         <v>46185</v>
       </c>
-      <c r="G9" s="5">
-        <v>18451</v>
+      <c r="G9" s="11">
+        <v>17076</v>
       </c>
       <c r="H9" s="12">
-        <v>46181.445833333331</v>
+        <v>46174.691180555557</v>
       </c>
       <c r="I9" s="16">
         <v>46181</v>
@@ -950,7 +950,7 @@
       <c r="J9" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -974,10 +974,10 @@
         <v>46185</v>
       </c>
       <c r="G10" s="11">
-        <v>17076</v>
+        <v>17252</v>
       </c>
       <c r="H10" s="12">
-        <v>46174.691180555557</v>
+        <v>46163.708333333336</v>
       </c>
       <c r="I10" s="16">
         <v>46181</v>
@@ -990,13 +990,13 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="5">
         <v>2026</v>
       </c>
       <c r="D11" s="10">
@@ -1008,11 +1008,11 @@
       <c r="F11" s="16">
         <v>46185</v>
       </c>
-      <c r="G11" s="11">
-        <v>17252</v>
+      <c r="G11" s="5">
+        <v>17749</v>
       </c>
       <c r="H11" s="12">
-        <v>46163.708333333336</v>
+        <v>46171.708333333336</v>
       </c>
       <c r="I11" s="16">
         <v>46181</v>
@@ -1044,10 +1044,10 @@
         <v>46185</v>
       </c>
       <c r="G12" s="5">
-        <v>17749</v>
+        <v>17866</v>
       </c>
       <c r="H12" s="12">
-        <v>46171.708333333336</v>
+        <v>46175.341215277775</v>
       </c>
       <c r="I12" s="16">
         <v>46181</v>
@@ -1055,7 +1055,7 @@
       <c r="J12" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1079,10 +1079,10 @@
         <v>46185</v>
       </c>
       <c r="G13" s="5">
-        <v>17866</v>
+        <v>17997</v>
       </c>
       <c r="H13" s="12">
-        <v>46175.341215277775</v>
+        <v>46175.708333333336</v>
       </c>
       <c r="I13" s="16">
         <v>46181</v>
@@ -1114,7 +1114,7 @@
         <v>46185</v>
       </c>
       <c r="G14" s="5">
-        <v>17997</v>
+        <v>18006</v>
       </c>
       <c r="H14" s="12">
         <v>46175.708333333336</v>
@@ -1149,10 +1149,10 @@
         <v>46185</v>
       </c>
       <c r="G15" s="5">
-        <v>18006</v>
+        <v>18176</v>
       </c>
       <c r="H15" s="12">
-        <v>46175.708333333336</v>
+        <v>46177.335069444445</v>
       </c>
       <c r="I15" s="16">
         <v>46181</v>
@@ -1184,10 +1184,10 @@
         <v>46185</v>
       </c>
       <c r="G16" s="5">
-        <v>18176</v>
+        <v>18275</v>
       </c>
       <c r="H16" s="12">
-        <v>46177.335069444445</v>
+        <v>46177.708333333336</v>
       </c>
       <c r="I16" s="16">
         <v>46181</v>
@@ -1219,10 +1219,10 @@
         <v>46185</v>
       </c>
       <c r="G17" s="5">
-        <v>18275</v>
+        <v>18333</v>
       </c>
       <c r="H17" s="12">
-        <v>46177.708333333336</v>
+        <v>46178.44940972222</v>
       </c>
       <c r="I17" s="16">
         <v>46181</v>
@@ -1254,10 +1254,10 @@
         <v>46185</v>
       </c>
       <c r="G18" s="5">
-        <v>18333</v>
+        <v>18339</v>
       </c>
       <c r="H18" s="12">
-        <v>46178.44940972222</v>
+        <v>46178.45815972222</v>
       </c>
       <c r="I18" s="16">
         <v>46181</v>
@@ -1289,10 +1289,10 @@
         <v>46185</v>
       </c>
       <c r="G19" s="5">
-        <v>18339</v>
+        <v>18385</v>
       </c>
       <c r="H19" s="12">
-        <v>46178.45815972222</v>
+        <v>46177.666134259256</v>
       </c>
       <c r="I19" s="16">
         <v>46181</v>
@@ -1324,10 +1324,10 @@
         <v>46185</v>
       </c>
       <c r="G20" s="5">
-        <v>18385</v>
+        <v>18403</v>
       </c>
       <c r="H20" s="12">
-        <v>46177.666134259256</v>
+        <v>46178.708333333336</v>
       </c>
       <c r="I20" s="16">
         <v>46181</v>
@@ -1359,10 +1359,10 @@
         <v>46185</v>
       </c>
       <c r="G21" s="5">
-        <v>18403</v>
+        <v>18434</v>
       </c>
       <c r="H21" s="12">
-        <v>46178.708333333336</v>
+        <v>46181.369317129633</v>
       </c>
       <c r="I21" s="16">
         <v>46181</v>
@@ -1394,10 +1394,10 @@
         <v>46185</v>
       </c>
       <c r="G22" s="5">
-        <v>18434</v>
+        <v>18450</v>
       </c>
       <c r="H22" s="12">
-        <v>46181.369317129633</v>
+        <v>46181.445613425924</v>
       </c>
       <c r="I22" s="16">
         <v>46181</v>
@@ -1429,10 +1429,10 @@
         <v>46185</v>
       </c>
       <c r="G23" s="5">
-        <v>18450</v>
+        <v>18460</v>
       </c>
       <c r="H23" s="12">
-        <v>46181.445613425924</v>
+        <v>46181.507349537038</v>
       </c>
       <c r="I23" s="16">
         <v>46181</v>
@@ -1449,7 +1449,7 @@
         <v>4</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C24" s="5">
         <v>2026</v>
@@ -1464,10 +1464,10 @@
         <v>46185</v>
       </c>
       <c r="G24" s="5">
-        <v>18460</v>
+        <v>18407</v>
       </c>
       <c r="H24" s="12">
-        <v>46181.507349537038</v>
+        <v>46178.495833333334</v>
       </c>
       <c r="I24" s="16">
         <v>46181</v>
@@ -1480,13 +1480,13 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="5">
+      <c r="B25" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="11">
         <v>2026</v>
       </c>
       <c r="D25" s="10">
@@ -1498,11 +1498,11 @@
       <c r="F25" s="16">
         <v>46185</v>
       </c>
-      <c r="G25" s="5">
-        <v>18407</v>
+      <c r="G25" s="11">
+        <v>17608</v>
       </c>
       <c r="H25" s="12">
-        <v>46178.495833333334</v>
+        <v>46169.551574074074</v>
       </c>
       <c r="I25" s="16">
         <v>46181</v>
@@ -1510,49 +1510,14 @@
       <c r="J25" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K25" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="11">
-        <v>2026</v>
-      </c>
-      <c r="D26" s="10">
-        <v>22</v>
-      </c>
-      <c r="E26" s="16">
-        <v>46181</v>
-      </c>
-      <c r="F26" s="16">
-        <v>46185</v>
-      </c>
-      <c r="G26" s="11">
-        <v>17608</v>
-      </c>
-      <c r="H26" s="12">
-        <v>46169.551574074074</v>
-      </c>
-      <c r="I26" s="16">
-        <v>46181</v>
-      </c>
-      <c r="J26" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K32" xr:uid="{05C2F3D6-88A9-4A6C-8904-EE71E1E2FD4B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K32">
-      <sortCondition ref="B1:B32"/>
+  <autoFilter ref="A1:K31" xr:uid="{05C2F3D6-88A9-4A6C-8904-EE71E1E2FD4B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K31">
+      <sortCondition ref="B1:B31"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1562,7 +1527,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A01383FE-69B8-4AB3-AF26-C199A6A7A8A1}">
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="9" bestFit="1" customWidth="1"/>
@@ -2944,6 +2909,41 @@
         <v>1</v>
       </c>
     </row>
+    <row r="40" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D40" s="10">
+        <v>22</v>
+      </c>
+      <c r="E40" s="16">
+        <v>46181</v>
+      </c>
+      <c r="F40" s="16">
+        <v>46185</v>
+      </c>
+      <c r="G40" s="5">
+        <v>18346</v>
+      </c>
+      <c r="H40" s="12">
+        <v>46178.538541666669</v>
+      </c>
+      <c r="I40" s="16">
+        <v>46181</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K39" xr:uid="{A01383FE-69B8-4AB3-AF26-C199A6A7A8A1}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
